--- a/Gestion du projet.xlsx
+++ b/Gestion du projet.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="6"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\OneDrive\Documents\HotelPlageSante\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECDAB7F-E8B2-459E-888B-2B5832687681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -20,68 +36,70 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
-  <si>
-    <t xml:space="preserve">Nom du projet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date de remise du projet: 14 octobre 2026 avant 23h55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tâche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durée prévue (h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durée réelle (h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalon 1 : Cahier d'analyse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rédaction et mise en page du document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réalisation du MPD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bolu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">..</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finalisation du document et correction avec Antidote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creation du script SQL pour les tables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Nom du projet</t>
+  </si>
+  <si>
+    <t>Date de remise du projet: 14 octobre 2026 avant 23h55</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Tâche</t>
+  </si>
+  <si>
+    <t>Durée prévue (h)</t>
+  </si>
+  <si>
+    <t>Durée réelle (h)</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Jalon 1 : Cahier d'analyse</t>
+  </si>
+  <si>
+    <t>Rédaction et mise en page du document</t>
+  </si>
+  <si>
+    <t>Ken</t>
+  </si>
+  <si>
+    <t>Réalisation du MPD</t>
+  </si>
+  <si>
+    <t>Bolu</t>
+  </si>
+  <si>
+    <t>..</t>
+  </si>
+  <si>
+    <t>Finalisation du document et correction avec Antidote</t>
+  </si>
+  <si>
+    <t>Creation du script SQL pour les tables</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>Ken + George</t>
+  </si>
+  <si>
+    <t>George</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,22 +108,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="26"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -113,7 +116,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -130,19 +133,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999"/>
+        <fgColor theme="4" tint="0.79989013336588644"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.15"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor rgb="FFDEEBF7"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -150,85 +153,38 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -287,13 +243,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -335,7 +307,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -370,7 +342,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -432,7 +404,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -456,7 +428,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -516,152 +488,151 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="8.8671875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="15.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="13.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.79"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="5" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="9" t="n">
-        <f aca="false">SUM(C7:C9)</f>
+      <c r="C6" s="8">
+        <f>SUM(C7:C9)</f>
         <v>3.5</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <f aca="false">SUM(D7:D9)</f>
+      <c r="D6" s="8">
+        <f>SUM(D7:D9)</f>
         <v>5.5</v>
       </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46286</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3">
         <v>1.5</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>46287</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+    <row r="15" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
         <v>15</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" s="8" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -669,12 +640,7 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A3:F3"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Gestion du projet.xlsx
+++ b/Gestion du projet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\OneDrive\Documents\HotelPlageSante\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECDAB7F-E8B2-459E-888B-2B5832687681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E049C08-BFEF-4C3C-94D0-C5EF44CD4AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-13380" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -74,9 +74,6 @@
     <t>Bolu</t>
   </si>
   <si>
-    <t>..</t>
-  </si>
-  <si>
     <t>Finalisation du document et correction avec Antidote</t>
   </si>
   <si>
@@ -90,6 +87,9 @@
   </si>
   <si>
     <t>George</t>
+  </si>
+  <si>
+    <t>1h-2h</t>
   </si>
 </sst>
 </file>
@@ -156,14 +156,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -179,6 +173,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,101 +507,101 @@
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="44.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="52.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <f>SUM(C7:C9)</f>
         <v>3.5</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <f>SUM(D7:D9)</f>
         <v>5.5</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="7">
         <v>46286</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="1">
         <v>1</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
         <v>1.5</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="7">
         <v>46287</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
         <v>3</v>
       </c>
       <c r="E8" t="s">
@@ -605,34 +609,43 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
+        <v>46288</v>
+      </c>
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C10" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>14</v>
+      <c r="D10" s="1">
+        <v>3</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
